--- a/artifacts/demo_simples_2027_puro_vs_hibrido.xlsx
+++ b/artifacts/demo_simples_2027_puro_vs_hibrido.xlsx
@@ -423,73 +423,7 @@
 </file>
 
 <file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="tbl_FISCAL_RESULTADOS_OPERACAO" displayName="tbl_FISCAL_RESULTADOS_OPERACAO" ref="A1:I1" headerRowCount="1">
-  <autoFilter ref="A1:I1"/>
-  <tableColumns count="9">
-    <tableColumn id="1" name="ID_CENARIO"/>
-    <tableColumn id="2" name="ID_EVENTO"/>
-    <tableColumn id="3" name="TRIBUTO"/>
-    <tableColumn id="4" name="INCIDE"/>
-    <tableColumn id="5" name="BASE"/>
-    <tableColumn id="6" name="ALIQUOTA"/>
-    <tableColumn id="7" name="CREDITO"/>
-    <tableColumn id="8" name="DEBITO"/>
-    <tableColumn id="9" name="VERSAO_REGRA"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tbl_ENTIDADE" displayName="tbl_ENTIDADE" ref="A1:E7" headerRowCount="1">
-  <autoFilter ref="A1:E7"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="ID_ENTIDADE"/>
-    <tableColumn id="2" name="ATRIBUTO"/>
-    <tableColumn id="3" name="VALOR"/>
-    <tableColumn id="4" name="TIPO_VALOR"/>
-    <tableColumn id="5" name="ORIGEM"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="tbl_FISCAL_APURACAO" displayName="tbl_FISCAL_APURACAO" ref="A1:H1" headerRowCount="1">
-  <autoFilter ref="A1:H1"/>
-  <tableColumns count="8">
-    <tableColumn id="1" name="ID_CENARIO"/>
-    <tableColumn id="2" name="TRIBUTO"/>
-    <tableColumn id="3" name="S_APUR"/>
-    <tableColumn id="4" name="T_RECOLHER"/>
-    <tableColumn id="5" name="P_CASH"/>
-    <tableColumn id="6" name="E_DRE"/>
-    <tableColumn id="7" name="C_SALDO"/>
-    <tableColumn id="8" name="VERSAO_REGRA"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="tbl_COMPARATIVO_CENARIOS" displayName="tbl_COMPARATIVO_CENARIOS" ref="A1:H1" headerRowCount="1">
-  <autoFilter ref="A1:H1"/>
-  <tableColumns count="8">
-    <tableColumn id="1" name="ID_CENARIO_BASE"/>
-    <tableColumn id="2" name="ID_CENARIO"/>
-    <tableColumn id="3" name="TRIBUTO"/>
-    <tableColumn id="4" name="DELTA_S_APUR"/>
-    <tableColumn id="5" name="DELTA_T_RECOLHER"/>
-    <tableColumn id="6" name="DELTA_P_CASH"/>
-    <tableColumn id="7" name="DELTA_E_DRE"/>
-    <tableColumn id="8" name="DELTA_C_SALDO"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
-</file>
-
-<file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="tbl_SIMPLES_2027_RESULTADOS" displayName="tbl_SIMPLES_2027_RESULTADOS" ref="A1:AA3" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="tbl_SIMPLES_2027_RESULTADOS" displayName="tbl_SIMPLES_2027_RESULTADOS" ref="A1:AA3" headerRowCount="1">
   <autoFilter ref="A1:AA3"/>
   <tableColumns count="27">
     <tableColumn id="1" name="ID_CENARIO"/>
@@ -524,8 +458,22 @@
 </table>
 </file>
 
-<file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="tbl_SIMPLES_2027_COMPARACAO" displayName="tbl_SIMPLES_2027_COMPARACAO" ref="A1:H6" headerRowCount="1">
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="tbl_ENTIDADE" displayName="tbl_ENTIDADE" ref="A1:E7" headerRowCount="1">
+  <autoFilter ref="A1:E7"/>
+  <tableColumns count="5">
+    <tableColumn id="1" name="ID_ENTIDADE"/>
+    <tableColumn id="2" name="ATRIBUTO"/>
+    <tableColumn id="3" name="VALOR"/>
+    <tableColumn id="4" name="TIPO_VALOR"/>
+    <tableColumn id="5" name="ORIGEM"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="tbl_SIMPLES_2027_COMPARACAO" displayName="tbl_SIMPLES_2027_COMPARACAO" ref="A1:H6" headerRowCount="1">
   <autoFilter ref="A1:H6"/>
   <tableColumns count="8">
     <tableColumn id="1" name="ID_CENARIO_BASE"/>
@@ -541,8 +489,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="tbl_VALIDACOES" displayName="tbl_VALIDACOES" ref="A1:K14" headerRowCount="1">
+<file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="tbl_VALIDACOES" displayName="tbl_VALIDACOES" ref="A1:K14" headerRowCount="1">
   <autoFilter ref="A1:K14"/>
   <tableColumns count="11">
     <tableColumn id="1" name="ETAPA"/>
@@ -561,8 +509,8 @@
 </table>
 </file>
 
-<file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="tbl_PROVENIENCIA" displayName="tbl_PROVENIENCIA" ref="A1:B19" headerRowCount="1">
+<file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="tbl_PROVENIENCIA" displayName="tbl_PROVENIENCIA" ref="A1:B19" headerRowCount="1">
   <autoFilter ref="A1:B19"/>
   <tableColumns count="2">
     <tableColumn id="1" name="CHAVE"/>
@@ -7501,7 +7449,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>https://www.in.gov.br/web/dou/-/resolucao-cgsn-n-190-de-2026</t>
+          <t>https://www.in.gov.br/web/dou/-/resolucao-cgsn-n-190-de-4-de-agosto-de-2026-724454118</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -7518,7 +7466,7 @@
         <v>46388</v>
       </c>
       <c r="N2" s="12" t="n">
-        <v>46568</v>
+        <v>47118</v>
       </c>
       <c r="O2" s="12" t="n">
         <v>46267</v>
@@ -7577,7 +7525,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>https://www.in.gov.br/web/dou/-/resolucao-cgsn-n-190-de-2026</t>
+          <t>https://www.in.gov.br/web/dou/-/resolucao-cgsn-n-190-de-4-de-agosto-de-2026-724454118</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -7594,7 +7542,7 @@
         <v>46388</v>
       </c>
       <c r="N3" s="12" t="n">
-        <v>46568</v>
+        <v>47118</v>
       </c>
       <c r="O3" s="12" t="n">
         <v>46267</v>
@@ -7653,7 +7601,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>https://www.in.gov.br/web/dou/-/resolucao-cgsn-n-190-de-2026</t>
+          <t>https://www.in.gov.br/web/dou/-/resolucao-cgsn-n-190-de-4-de-agosto-de-2026-724454118</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -7670,7 +7618,7 @@
         <v>46388</v>
       </c>
       <c r="N4" s="12" t="n">
-        <v>46568</v>
+        <v>47118</v>
       </c>
       <c r="O4" s="12" t="n">
         <v>46267</v>
@@ -7729,7 +7677,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>https://www.in.gov.br/web/dou/-/resolucao-cgsn-n-190-de-2026</t>
+          <t>https://www.in.gov.br/web/dou/-/resolucao-cgsn-n-190-de-4-de-agosto-de-2026-724454118</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -7746,7 +7694,7 @@
         <v>46388</v>
       </c>
       <c r="N5" s="12" t="n">
-        <v>46568</v>
+        <v>47118</v>
       </c>
       <c r="O5" s="12" t="n">
         <v>46267</v>
@@ -7805,7 +7753,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>https://www.in.gov.br/web/dou/-/resolucao-cgsn-n-190-de-2026</t>
+          <t>https://www.in.gov.br/web/dou/-/resolucao-cgsn-n-190-de-4-de-agosto-de-2026-724454118</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -7822,7 +7770,7 @@
         <v>46388</v>
       </c>
       <c r="N6" s="12" t="n">
-        <v>46568</v>
+        <v>47118</v>
       </c>
       <c r="O6" s="12" t="n">
         <v>46267</v>
@@ -7881,7 +7829,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>https://www.in.gov.br/web/dou/-/resolucao-cgsn-n-190-de-2026</t>
+          <t>https://www.in.gov.br/web/dou/-/resolucao-cgsn-n-190-de-4-de-agosto-de-2026-724454118</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -7898,7 +7846,7 @@
         <v>46388</v>
       </c>
       <c r="N7" s="12" t="n">
-        <v>46568</v>
+        <v>47118</v>
       </c>
       <c r="O7" s="12" t="n">
         <v>46267</v>
@@ -7957,7 +7905,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>https://www.in.gov.br/web/dou/-/resolucao-cgsn-n-190-de-2026</t>
+          <t>https://www.in.gov.br/web/dou/-/resolucao-cgsn-n-190-de-4-de-agosto-de-2026-724454118</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -7974,7 +7922,7 @@
         <v>46388</v>
       </c>
       <c r="N8" s="12" t="n">
-        <v>46568</v>
+        <v>47118</v>
       </c>
       <c r="O8" s="12" t="n">
         <v>46267</v>
@@ -8033,7 +7981,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>https://www.in.gov.br/web/dou/-/resolucao-cgsn-n-190-de-2026</t>
+          <t>https://www.in.gov.br/web/dou/-/resolucao-cgsn-n-190-de-4-de-agosto-de-2026-724454118</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -8050,7 +7998,7 @@
         <v>46388</v>
       </c>
       <c r="N9" s="12" t="n">
-        <v>46568</v>
+        <v>47118</v>
       </c>
       <c r="O9" s="12" t="n">
         <v>46267</v>
@@ -8109,7 +8057,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>https://www.in.gov.br/web/dou/-/resolucao-cgsn-n-190-de-2026</t>
+          <t>https://www.in.gov.br/web/dou/-/resolucao-cgsn-n-190-de-4-de-agosto-de-2026-724454118</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -8126,7 +8074,7 @@
         <v>46388</v>
       </c>
       <c r="N10" s="12" t="n">
-        <v>46568</v>
+        <v>47118</v>
       </c>
       <c r="O10" s="12" t="n">
         <v>46267</v>
@@ -8185,7 +8133,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://www.in.gov.br/web/dou/-/resolucao-cgsn-n-190-de-2026</t>
+          <t>https://www.in.gov.br/web/dou/-/resolucao-cgsn-n-190-de-4-de-agosto-de-2026-724454118</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -8202,7 +8150,7 @@
         <v>46388</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>46568</v>
+        <v>47118</v>
       </c>
       <c r="O11" s="12" t="n">
         <v>46267</v>
@@ -8261,7 +8209,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>https://www.in.gov.br/web/dou/-/resolucao-cgsn-n-190-de-2026</t>
+          <t>https://www.in.gov.br/web/dou/-/resolucao-cgsn-n-190-de-4-de-agosto-de-2026-724454118</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -8278,7 +8226,7 @@
         <v>46388</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>46568</v>
+        <v>47118</v>
       </c>
       <c r="O12" s="12" t="n">
         <v>46267</v>
@@ -8337,7 +8285,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>https://www.in.gov.br/web/dou/-/resolucao-cgsn-n-190-de-2026</t>
+          <t>https://www.in.gov.br/web/dou/-/resolucao-cgsn-n-190-de-4-de-agosto-de-2026-724454118</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -8354,7 +8302,7 @@
         <v>46388</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>46568</v>
+        <v>47118</v>
       </c>
       <c r="O13" s="12" t="n">
         <v>46267</v>
@@ -8413,7 +8361,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>https://www.in.gov.br/web/dou/-/resolucao-cgsn-n-190-de-2026</t>
+          <t>https://www.in.gov.br/web/dou/-/resolucao-cgsn-n-190-de-4-de-agosto-de-2026-724454118</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -8430,7 +8378,7 @@
         <v>46388</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>46568</v>
+        <v>47118</v>
       </c>
       <c r="O14" s="12" t="n">
         <v>46267</v>
@@ -8489,7 +8437,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>https://www.in.gov.br/web/dou/-/resolucao-cgsn-n-190-de-2026</t>
+          <t>https://www.in.gov.br/web/dou/-/resolucao-cgsn-n-190-de-4-de-agosto-de-2026-724454118</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -8506,7 +8454,7 @@
         <v>46388</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>46568</v>
+        <v>47118</v>
       </c>
       <c r="O15" s="12" t="n">
         <v>46267</v>
@@ -8565,7 +8513,7 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>https://www.in.gov.br/web/dou/-/resolucao-cgsn-n-190-de-2026</t>
+          <t>https://www.in.gov.br/web/dou/-/resolucao-cgsn-n-190-de-4-de-agosto-de-2026-724454118</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -8582,7 +8530,7 @@
         <v>46388</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>46568</v>
+        <v>47118</v>
       </c>
       <c r="O16" s="12" t="n">
         <v>46267</v>
@@ -8641,7 +8589,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>https://www.in.gov.br/web/dou/-/resolucao-cgsn-n-190-de-2026</t>
+          <t>https://www.in.gov.br/web/dou/-/resolucao-cgsn-n-190-de-4-de-agosto-de-2026-724454118</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -8658,7 +8606,7 @@
         <v>46388</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>46568</v>
+        <v>47118</v>
       </c>
       <c r="O17" s="12" t="n">
         <v>46267</v>
@@ -8717,7 +8665,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>https://www.in.gov.br/web/dou/-/resolucao-cgsn-n-190-de-2026</t>
+          <t>https://www.in.gov.br/web/dou/-/resolucao-cgsn-n-190-de-4-de-agosto-de-2026-724454118</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -8734,7 +8682,7 @@
         <v>46388</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>46568</v>
+        <v>47118</v>
       </c>
       <c r="O18" s="12" t="n">
         <v>46267</v>
@@ -8874,7 +8822,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>art. 348</t>
+          <t>art. 344</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -9094,9 +9042,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -9164,9 +9109,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
@@ -9234,9 +9176,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>
 
